--- a/data/Lakes/lake_coord_surface.xlsx
+++ b/data/Lakes/lake_coord_surface.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20407"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Ecologia\Documents\ARTICLES\NAT_FunMetaNET\data\Lakes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anna\OneDrive - Universitat de Girona\tesi\WP1 NATs\NAT_FunMetaNET\data\Lakes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC96C7DE-9592-482B-90B1-4FE4AAD3C43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_0E966FA0FDF16EF8391A607A968A384643685756" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{6BFCF2FF-4F49-4962-939D-829F42A9845A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19430" windowHeight="10430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="metadata" sheetId="4" r:id="rId1"/>
-    <sheet name="data" sheetId="3" r:id="rId2"/>
+    <sheet name="data" sheetId="3" r:id="rId1"/>
+    <sheet name="metadata" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -23,10 +23,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1090,9 +1090,1008 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9FBB724-03A9-4FBE-8A37-80E91269FD98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E57"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>14.272717030000001</v>
+      </c>
+      <c r="C2">
+        <v>57.175692580000003</v>
+      </c>
+      <c r="D2">
+        <v>33.5</v>
+      </c>
+      <c r="E2">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>16.369400290000002</v>
+      </c>
+      <c r="C3">
+        <v>59.094938020000001</v>
+      </c>
+      <c r="D3">
+        <v>30.94</v>
+      </c>
+      <c r="E3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>16.096321769999999</v>
+      </c>
+      <c r="C4">
+        <v>57.947945109999999</v>
+      </c>
+      <c r="D4">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="E4">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>12.50201227</v>
+      </c>
+      <c r="C5">
+        <v>58.31509784</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>14.377527410000001</v>
+      </c>
+      <c r="C6">
+        <v>56.246004550000002</v>
+      </c>
+      <c r="D6">
+        <v>50.53</v>
+      </c>
+      <c r="E6">
+        <v>9.39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>18.93602143</v>
+      </c>
+      <c r="C7">
+        <v>57.915651680000003</v>
+      </c>
+      <c r="D7">
+        <v>656.5</v>
+      </c>
+      <c r="E7">
+        <v>16.829999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>20.438731369999999</v>
+      </c>
+      <c r="C8">
+        <v>64.23888359</v>
+      </c>
+      <c r="D8">
+        <v>48.86</v>
+      </c>
+      <c r="E8">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>17.37018582</v>
+      </c>
+      <c r="C9">
+        <v>58.856165349999998</v>
+      </c>
+      <c r="D9">
+        <v>135.62</v>
+      </c>
+      <c r="E9">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>15.72807059</v>
+      </c>
+      <c r="C10">
+        <v>56.597202809999999</v>
+      </c>
+      <c r="D10">
+        <v>10.01</v>
+      </c>
+      <c r="E10">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <v>12.33991322</v>
+      </c>
+      <c r="C11">
+        <v>59.302379260000002</v>
+      </c>
+      <c r="D11">
+        <v>112.64</v>
+      </c>
+      <c r="E11">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>15.6866801</v>
+      </c>
+      <c r="C12">
+        <v>59.89696781</v>
+      </c>
+      <c r="D12">
+        <v>164.92</v>
+      </c>
+      <c r="E12">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>17.023012250000001</v>
+      </c>
+      <c r="C13">
+        <v>59.179151859999997</v>
+      </c>
+      <c r="D13">
+        <v>18.87</v>
+      </c>
+      <c r="E13">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>17.041553069999999</v>
+      </c>
+      <c r="C14">
+        <v>59.865211090000003</v>
+      </c>
+      <c r="D14">
+        <v>54.42</v>
+      </c>
+      <c r="E14">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>14.702844369999999</v>
+      </c>
+      <c r="C15">
+        <v>58.757759270000001</v>
+      </c>
+      <c r="D15">
+        <v>20.21</v>
+      </c>
+      <c r="E15">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>14.52958559</v>
+      </c>
+      <c r="C16">
+        <v>57.091988749999999</v>
+      </c>
+      <c r="D16">
+        <v>158.84</v>
+      </c>
+      <c r="E16">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>15.249297540000001</v>
+      </c>
+      <c r="C17">
+        <v>57.609093129999998</v>
+      </c>
+      <c r="D17">
+        <v>33.86</v>
+      </c>
+      <c r="E17">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>12.181194380000001</v>
+      </c>
+      <c r="C18">
+        <v>58.148151579999997</v>
+      </c>
+      <c r="D18">
+        <v>26.27</v>
+      </c>
+      <c r="E18">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>17.908103839999999</v>
+      </c>
+      <c r="C19">
+        <v>59.570669729999999</v>
+      </c>
+      <c r="D19">
+        <v>449.4</v>
+      </c>
+      <c r="E19">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>13.626456920000001</v>
+      </c>
+      <c r="C20">
+        <v>60.645047779999999</v>
+      </c>
+      <c r="D20">
+        <v>65.3</v>
+      </c>
+      <c r="E20">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>15.142132800000001</v>
+      </c>
+      <c r="C21">
+        <v>58.762567660000002</v>
+      </c>
+      <c r="D21">
+        <v>22.47</v>
+      </c>
+      <c r="E21">
+        <v>4.1900000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22">
+        <v>13.71142536</v>
+      </c>
+      <c r="C22">
+        <v>57.337246630000003</v>
+      </c>
+      <c r="D22">
+        <v>11.57</v>
+      </c>
+      <c r="E22">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <v>17.63305269</v>
+      </c>
+      <c r="C23">
+        <v>63.542733929999997</v>
+      </c>
+      <c r="D23">
+        <v>671.47</v>
+      </c>
+      <c r="E23">
+        <v>26.56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24">
+        <v>13.579214459999999</v>
+      </c>
+      <c r="C24">
+        <v>57.007390360000002</v>
+      </c>
+      <c r="D24">
+        <v>53.43</v>
+      </c>
+      <c r="E24">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25">
+        <v>13.35687085</v>
+      </c>
+      <c r="C25">
+        <v>55.487976400000001</v>
+      </c>
+      <c r="D25">
+        <v>51.58</v>
+      </c>
+      <c r="E25">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26">
+        <v>14.928576530000001</v>
+      </c>
+      <c r="C26">
+        <v>56.878100109999998</v>
+      </c>
+      <c r="D26">
+        <v>23.05</v>
+      </c>
+      <c r="E26">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27">
+        <v>15.2573361</v>
+      </c>
+      <c r="C27">
+        <v>57.051499069999998</v>
+      </c>
+      <c r="D27">
+        <v>125.48</v>
+      </c>
+      <c r="E27">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28">
+        <v>19.94364727</v>
+      </c>
+      <c r="C28">
+        <v>67.058964930000002</v>
+      </c>
+      <c r="D28">
+        <v>111.11</v>
+      </c>
+      <c r="E28">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29">
+        <v>13.47275316</v>
+      </c>
+      <c r="C29">
+        <v>55.708742999999998</v>
+      </c>
+      <c r="D29">
+        <v>273.61</v>
+      </c>
+      <c r="E29">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30">
+        <v>12.33679175</v>
+      </c>
+      <c r="C30">
+        <v>57.55726645</v>
+      </c>
+      <c r="D30">
+        <v>58.32</v>
+      </c>
+      <c r="E30">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31">
+        <v>14.53998621</v>
+      </c>
+      <c r="C31">
+        <v>56.206193900000002</v>
+      </c>
+      <c r="D31">
+        <v>3.44</v>
+      </c>
+      <c r="E31">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32">
+        <v>16.806479329999998</v>
+      </c>
+      <c r="C32">
+        <v>59.101733000000003</v>
+      </c>
+      <c r="D32">
+        <v>31.2</v>
+      </c>
+      <c r="E32">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33">
+        <v>14.52040379</v>
+      </c>
+      <c r="C33">
+        <v>59.586160120000002</v>
+      </c>
+      <c r="D33">
+        <v>112.26</v>
+      </c>
+      <c r="E33">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34">
+        <v>17.408631</v>
+      </c>
+      <c r="C34">
+        <v>59.16986155</v>
+      </c>
+      <c r="D34">
+        <v>1415.63</v>
+      </c>
+      <c r="E34">
+        <v>78.89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35">
+        <v>14.685101960000001</v>
+      </c>
+      <c r="C35">
+        <v>56.286360139999999</v>
+      </c>
+      <c r="D35">
+        <v>18.73</v>
+      </c>
+      <c r="E35">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>12.75795701</v>
+      </c>
+      <c r="C36">
+        <v>59.725678690000002</v>
+      </c>
+      <c r="D36">
+        <v>73.459999999999994</v>
+      </c>
+      <c r="E36">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37">
+        <v>13.33818071</v>
+      </c>
+      <c r="C37">
+        <v>59.89303932</v>
+      </c>
+      <c r="D37">
+        <v>37.340000000000003</v>
+      </c>
+      <c r="E37">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38">
+        <v>12.98413021</v>
+      </c>
+      <c r="C38">
+        <v>59.409458540000003</v>
+      </c>
+      <c r="D38">
+        <v>200.41</v>
+      </c>
+      <c r="E38">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39">
+        <v>15.550299799999999</v>
+      </c>
+      <c r="C39">
+        <v>59.837084859999997</v>
+      </c>
+      <c r="D39">
+        <v>177.53</v>
+      </c>
+      <c r="E39">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40">
+        <v>17.36908583</v>
+      </c>
+      <c r="C40">
+        <v>58.808594919999997</v>
+      </c>
+      <c r="D40">
+        <v>87.39</v>
+      </c>
+      <c r="E40">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41">
+        <v>15.35816369</v>
+      </c>
+      <c r="C41">
+        <v>56.325019949999998</v>
+      </c>
+      <c r="D41">
+        <f>100.99-1.9-1</f>
+        <v>98.089999999999989</v>
+      </c>
+      <c r="E41">
+        <f>6.87+0.53+0.57</f>
+        <v>7.9700000000000006</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42">
+        <v>16.23389749</v>
+      </c>
+      <c r="C42">
+        <v>58.763120479999998</v>
+      </c>
+      <c r="D42">
+        <v>16.54</v>
+      </c>
+      <c r="E42">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43">
+        <v>15.44527639</v>
+      </c>
+      <c r="C43">
+        <v>60.638792559999999</v>
+      </c>
+      <c r="D43">
+        <f>39.67-0.32</f>
+        <v>39.35</v>
+      </c>
+      <c r="E43">
+        <f>3.96+0.21</f>
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44">
+        <v>13.065325720000001</v>
+      </c>
+      <c r="C44">
+        <v>56.671505279999998</v>
+      </c>
+      <c r="D44">
+        <f>30.07-0.21-0.08</f>
+        <v>29.78</v>
+      </c>
+      <c r="E44">
+        <f>4.43+0.18+0.12</f>
+        <v>4.7299999999999995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45">
+        <v>16.575306680000001</v>
+      </c>
+      <c r="C45">
+        <v>61.642758569999998</v>
+      </c>
+      <c r="D45">
+        <v>53.32</v>
+      </c>
+      <c r="E45">
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46">
+        <v>17.353497170000001</v>
+      </c>
+      <c r="C46">
+        <v>59.114946590000002</v>
+      </c>
+      <c r="D46">
+        <f>37.85-0.12-0.15</f>
+        <v>37.580000000000005</v>
+      </c>
+      <c r="E46">
+        <f>4.38+0.14+0.16</f>
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47">
+        <v>17.6003504</v>
+      </c>
+      <c r="C47">
+        <v>64.598565170000001</v>
+      </c>
+      <c r="D47">
+        <f>721.73-0.26</f>
+        <v>721.47</v>
+      </c>
+      <c r="E47">
+        <f>19.89+0.29</f>
+        <v>20.18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48">
+        <v>15.271186139999999</v>
+      </c>
+      <c r="C48">
+        <v>56.947835859999998</v>
+      </c>
+      <c r="D48">
+        <v>35.909999999999997</v>
+      </c>
+      <c r="E48">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49">
+        <v>14.937211789999999</v>
+      </c>
+      <c r="C49">
+        <v>56.177464809999996</v>
+      </c>
+      <c r="D49">
+        <v>17.190000000000001</v>
+      </c>
+      <c r="E49">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50">
+        <v>20.262017589999999</v>
+      </c>
+      <c r="C50">
+        <v>64.061147680000005</v>
+      </c>
+      <c r="D50">
+        <f>232.47-0.67-0.07-0.08-0.11-0.63-0.19-0.27-0.07-0.07-0.07</f>
+        <v>230.24</v>
+      </c>
+      <c r="E50">
+        <f>12.47+0.31+0.1+0.11+0.13+0.3+0.2+0.2+0.1+0.1+0.1</f>
+        <v>14.12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51">
+        <v>15.059543400000001</v>
+      </c>
+      <c r="C51">
+        <v>57.463984529999998</v>
+      </c>
+      <c r="D51">
+        <v>16.63</v>
+      </c>
+      <c r="E51">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52">
+        <v>16.032840910000001</v>
+      </c>
+      <c r="C52">
+        <v>57.46609333</v>
+      </c>
+      <c r="D52">
+        <v>10.07</v>
+      </c>
+      <c r="E52">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53">
+        <v>18.36602534</v>
+      </c>
+      <c r="C53">
+        <v>59.557037999999999</v>
+      </c>
+      <c r="D53">
+        <f>103.49-0.74</f>
+        <v>102.75</v>
+      </c>
+      <c r="E53">
+        <f>12.84+0.37</f>
+        <v>13.209999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54">
+        <v>15.67327384</v>
+      </c>
+      <c r="C54">
+        <v>62.243529989999999</v>
+      </c>
+      <c r="D54">
+        <f>164.23-0.68-0.67</f>
+        <v>162.88</v>
+      </c>
+      <c r="E54">
+        <f>9.32+0.34+0.36</f>
+        <v>10.02</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55">
+        <v>12.293728870000001</v>
+      </c>
+      <c r="C55">
+        <v>59.60976084</v>
+      </c>
+      <c r="D55">
+        <f>51.65-0.18-0.4</f>
+        <v>51.07</v>
+      </c>
+      <c r="E55">
+        <f>4.8+0.17+0.55</f>
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56">
+        <v>16.987209159999999</v>
+      </c>
+      <c r="C56">
+        <v>62.330101769999999</v>
+      </c>
+      <c r="D56">
+        <v>42.52</v>
+      </c>
+      <c r="E56">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57">
+        <v>17.515287409999999</v>
+      </c>
+      <c r="C57">
+        <v>63.00245108</v>
+      </c>
+      <c r="D57">
+        <f>198.2-0.31</f>
+        <v>197.89</v>
+      </c>
+      <c r="E57">
+        <f>9.79+0.25</f>
+        <v>10.039999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="42" bestFit="1" customWidth="1"/>
   </cols>
@@ -1164,1003 +2163,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E05A277-D9F9-4D71-ABD4-4884D0686F0A}">
-  <dimension ref="A1:E57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>57.175692580000003</v>
-      </c>
-      <c r="C2">
-        <v>14.272717030000001</v>
-      </c>
-      <c r="D2">
-        <v>33.5</v>
-      </c>
-      <c r="E2">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>59.094938020000001</v>
-      </c>
-      <c r="C3">
-        <v>16.369400290000002</v>
-      </c>
-      <c r="D3">
-        <v>30.94</v>
-      </c>
-      <c r="E3">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>57.947945109999999</v>
-      </c>
-      <c r="C4">
-        <v>16.096321769999999</v>
-      </c>
-      <c r="D4">
-        <v>16.149999999999999</v>
-      </c>
-      <c r="E4">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>58.31509784</v>
-      </c>
-      <c r="C5">
-        <v>12.50201227</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>56.246004550000002</v>
-      </c>
-      <c r="C6">
-        <v>14.377527410000001</v>
-      </c>
-      <c r="D6">
-        <v>50.53</v>
-      </c>
-      <c r="E6">
-        <v>9.39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>57.915651680000003</v>
-      </c>
-      <c r="C7">
-        <v>18.93602143</v>
-      </c>
-      <c r="D7">
-        <v>656.5</v>
-      </c>
-      <c r="E7">
-        <v>16.829999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>64.23888359</v>
-      </c>
-      <c r="C8">
-        <v>20.438731369999999</v>
-      </c>
-      <c r="D8">
-        <v>48.86</v>
-      </c>
-      <c r="E8">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>58.856165349999998</v>
-      </c>
-      <c r="C9">
-        <v>17.37018582</v>
-      </c>
-      <c r="D9">
-        <v>135.62</v>
-      </c>
-      <c r="E9">
-        <v>7.88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
-        <v>56.597202809999999</v>
-      </c>
-      <c r="C10">
-        <v>15.72807059</v>
-      </c>
-      <c r="D10">
-        <v>10.01</v>
-      </c>
-      <c r="E10">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11">
-        <v>59.302379260000002</v>
-      </c>
-      <c r="C11">
-        <v>12.33991322</v>
-      </c>
-      <c r="D11">
-        <v>112.64</v>
-      </c>
-      <c r="E11">
-        <v>8.23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>59.89696781</v>
-      </c>
-      <c r="C12">
-        <v>15.6866801</v>
-      </c>
-      <c r="D12">
-        <v>164.92</v>
-      </c>
-      <c r="E12">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13">
-        <v>59.179151859999997</v>
-      </c>
-      <c r="C13">
-        <v>17.023012250000001</v>
-      </c>
-      <c r="D13">
-        <v>18.87</v>
-      </c>
-      <c r="E13">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <v>59.865211090000003</v>
-      </c>
-      <c r="C14">
-        <v>17.041553069999999</v>
-      </c>
-      <c r="D14">
-        <v>54.42</v>
-      </c>
-      <c r="E14">
-        <v>4.42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15">
-        <v>58.757759270000001</v>
-      </c>
-      <c r="C15">
-        <v>14.702844369999999</v>
-      </c>
-      <c r="D15">
-        <v>20.21</v>
-      </c>
-      <c r="E15">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16">
-        <v>57.091988749999999</v>
-      </c>
-      <c r="C16">
-        <v>14.52958559</v>
-      </c>
-      <c r="D16">
-        <v>158.84</v>
-      </c>
-      <c r="E16">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17">
-        <v>57.609093129999998</v>
-      </c>
-      <c r="C17">
-        <v>15.249297540000001</v>
-      </c>
-      <c r="D17">
-        <v>33.86</v>
-      </c>
-      <c r="E17">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18">
-        <v>58.148151579999997</v>
-      </c>
-      <c r="C18">
-        <v>12.181194380000001</v>
-      </c>
-      <c r="D18">
-        <v>26.27</v>
-      </c>
-      <c r="E18">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19">
-        <v>59.570669729999999</v>
-      </c>
-      <c r="C19">
-        <v>17.908103839999999</v>
-      </c>
-      <c r="D19">
-        <v>449.4</v>
-      </c>
-      <c r="E19">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
-        <v>60.645047779999999</v>
-      </c>
-      <c r="C20">
-        <v>13.626456920000001</v>
-      </c>
-      <c r="D20">
-        <v>65.3</v>
-      </c>
-      <c r="E20">
-        <v>5.91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21">
-        <v>58.762567660000002</v>
-      </c>
-      <c r="C21">
-        <v>15.142132800000001</v>
-      </c>
-      <c r="D21">
-        <v>22.47</v>
-      </c>
-      <c r="E21">
-        <v>4.1900000000000004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22">
-        <v>57.337246630000003</v>
-      </c>
-      <c r="C22">
-        <v>13.71142536</v>
-      </c>
-      <c r="D22">
-        <v>11.57</v>
-      </c>
-      <c r="E22">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23">
-        <v>63.542733929999997</v>
-      </c>
-      <c r="C23">
-        <v>17.63305269</v>
-      </c>
-      <c r="D23">
-        <v>671.47</v>
-      </c>
-      <c r="E23">
-        <v>26.56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24">
-        <v>57.007390360000002</v>
-      </c>
-      <c r="C24">
-        <v>13.579214459999999</v>
-      </c>
-      <c r="D24">
-        <v>53.43</v>
-      </c>
-      <c r="E24">
-        <v>6.36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>55.487976400000001</v>
-      </c>
-      <c r="C25">
-        <v>13.35687085</v>
-      </c>
-      <c r="D25">
-        <v>51.58</v>
-      </c>
-      <c r="E25">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26">
-        <v>56.878100109999998</v>
-      </c>
-      <c r="C26">
-        <v>14.928576530000001</v>
-      </c>
-      <c r="D26">
-        <v>23.05</v>
-      </c>
-      <c r="E26">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27">
-        <v>57.051499069999998</v>
-      </c>
-      <c r="C27">
-        <v>15.2573361</v>
-      </c>
-      <c r="D27">
-        <v>125.48</v>
-      </c>
-      <c r="E27">
-        <v>6.67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28">
-        <v>67.058964930000002</v>
-      </c>
-      <c r="C28">
-        <v>19.94364727</v>
-      </c>
-      <c r="D28">
-        <v>111.11</v>
-      </c>
-      <c r="E28">
-        <v>5.82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29">
-        <v>55.708742999999998</v>
-      </c>
-      <c r="C29">
-        <v>13.47275316</v>
-      </c>
-      <c r="D29">
-        <v>273.61</v>
-      </c>
-      <c r="E29">
-        <v>8.69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30">
-        <v>57.55726645</v>
-      </c>
-      <c r="C30">
-        <v>12.33679175</v>
-      </c>
-      <c r="D30">
-        <v>58.32</v>
-      </c>
-      <c r="E30">
-        <v>6.97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31">
-        <v>56.206193900000002</v>
-      </c>
-      <c r="C31">
-        <v>14.53998621</v>
-      </c>
-      <c r="D31">
-        <v>3.44</v>
-      </c>
-      <c r="E31">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32">
-        <v>59.101733000000003</v>
-      </c>
-      <c r="C32">
-        <v>16.806479329999998</v>
-      </c>
-      <c r="D32">
-        <v>31.2</v>
-      </c>
-      <c r="E32">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33">
-        <v>59.586160120000002</v>
-      </c>
-      <c r="C33">
-        <v>14.52040379</v>
-      </c>
-      <c r="D33">
-        <v>112.26</v>
-      </c>
-      <c r="E33">
-        <v>6.01</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34">
-        <v>59.16986155</v>
-      </c>
-      <c r="C34">
-        <v>17.408631</v>
-      </c>
-      <c r="D34">
-        <v>1415.63</v>
-      </c>
-      <c r="E34">
-        <v>78.89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35">
-        <v>56.286360139999999</v>
-      </c>
-      <c r="C35">
-        <v>14.685101960000001</v>
-      </c>
-      <c r="D35">
-        <v>18.73</v>
-      </c>
-      <c r="E35">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36">
-        <v>59.725678690000002</v>
-      </c>
-      <c r="C36">
-        <v>12.75795701</v>
-      </c>
-      <c r="D36">
-        <v>73.459999999999994</v>
-      </c>
-      <c r="E36">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37">
-        <v>59.89303932</v>
-      </c>
-      <c r="C37">
-        <v>13.33818071</v>
-      </c>
-      <c r="D37">
-        <v>37.340000000000003</v>
-      </c>
-      <c r="E37">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38">
-        <v>59.409458540000003</v>
-      </c>
-      <c r="C38">
-        <v>12.98413021</v>
-      </c>
-      <c r="D38">
-        <v>200.41</v>
-      </c>
-      <c r="E38">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39">
-        <v>59.837084859999997</v>
-      </c>
-      <c r="C39">
-        <v>15.550299799999999</v>
-      </c>
-      <c r="D39">
-        <v>177.53</v>
-      </c>
-      <c r="E39">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40">
-        <v>58.808594919999997</v>
-      </c>
-      <c r="C40">
-        <v>17.36908583</v>
-      </c>
-      <c r="D40">
-        <v>87.39</v>
-      </c>
-      <c r="E40">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41">
-        <v>56.325019949999998</v>
-      </c>
-      <c r="C41">
-        <v>15.35816369</v>
-      </c>
-      <c r="D41">
-        <f>100.99-1.9-1</f>
-        <v>98.089999999999989</v>
-      </c>
-      <c r="E41">
-        <f>6.87+0.53+0.57</f>
-        <v>7.9700000000000006</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42">
-        <v>58.763120479999998</v>
-      </c>
-      <c r="C42">
-        <v>16.23389749</v>
-      </c>
-      <c r="D42">
-        <v>16.54</v>
-      </c>
-      <c r="E42">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43">
-        <v>60.638792559999999</v>
-      </c>
-      <c r="C43">
-        <v>15.44527639</v>
-      </c>
-      <c r="D43">
-        <f>39.67-0.32</f>
-        <v>39.35</v>
-      </c>
-      <c r="E43">
-        <f>3.96+0.21</f>
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44">
-        <v>56.671505279999998</v>
-      </c>
-      <c r="C44">
-        <v>13.065325720000001</v>
-      </c>
-      <c r="D44">
-        <f>30.07-0.21-0.08</f>
-        <v>29.78</v>
-      </c>
-      <c r="E44">
-        <f>4.43+0.18+0.12</f>
-        <v>4.7299999999999995</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45">
-        <v>61.642758569999998</v>
-      </c>
-      <c r="C45">
-        <v>16.575306680000001</v>
-      </c>
-      <c r="D45">
-        <v>53.32</v>
-      </c>
-      <c r="E45">
-        <v>4.07</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46">
-        <v>59.114946590000002</v>
-      </c>
-      <c r="C46">
-        <v>17.353497170000001</v>
-      </c>
-      <c r="D46">
-        <f>37.85-0.12-0.15</f>
-        <v>37.580000000000005</v>
-      </c>
-      <c r="E46">
-        <f>4.38+0.14+0.16</f>
-        <v>4.68</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47">
-        <v>64.598565170000001</v>
-      </c>
-      <c r="C47">
-        <v>17.6003504</v>
-      </c>
-      <c r="D47">
-        <f>721.73-0.26</f>
-        <v>721.47</v>
-      </c>
-      <c r="E47">
-        <f>19.89+0.29</f>
-        <v>20.18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48">
-        <v>56.947835859999998</v>
-      </c>
-      <c r="C48">
-        <v>15.271186139999999</v>
-      </c>
-      <c r="D48">
-        <v>35.909999999999997</v>
-      </c>
-      <c r="E48">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49">
-        <v>56.177464809999996</v>
-      </c>
-      <c r="C49">
-        <v>14.937211789999999</v>
-      </c>
-      <c r="D49">
-        <v>17.190000000000001</v>
-      </c>
-      <c r="E49">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50">
-        <v>64.061147680000005</v>
-      </c>
-      <c r="C50">
-        <v>20.262017589999999</v>
-      </c>
-      <c r="D50">
-        <f>232.47-0.67-0.07-0.08-0.11-0.63-0.19-0.27-0.07-0.07-0.07</f>
-        <v>230.24</v>
-      </c>
-      <c r="E50">
-        <f>12.47+0.31+0.1+0.11+0.13+0.3+0.2+0.2+0.1+0.1+0.1</f>
-        <v>14.12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51">
-        <v>57.463984529999998</v>
-      </c>
-      <c r="C51">
-        <v>15.059543400000001</v>
-      </c>
-      <c r="D51">
-        <v>16.63</v>
-      </c>
-      <c r="E51">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52">
-        <v>57.46609333</v>
-      </c>
-      <c r="C52">
-        <v>16.032840910000001</v>
-      </c>
-      <c r="D52">
-        <v>10.07</v>
-      </c>
-      <c r="E52">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53">
-        <v>59.557037999999999</v>
-      </c>
-      <c r="C53">
-        <v>18.36602534</v>
-      </c>
-      <c r="D53">
-        <f>103.49-0.74</f>
-        <v>102.75</v>
-      </c>
-      <c r="E53">
-        <f>12.84+0.37</f>
-        <v>13.209999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54">
-        <v>62.243529989999999</v>
-      </c>
-      <c r="C54">
-        <v>15.67327384</v>
-      </c>
-      <c r="D54">
-        <f>164.23-0.68-0.67</f>
-        <v>162.88</v>
-      </c>
-      <c r="E54">
-        <f>9.32+0.34+0.36</f>
-        <v>10.02</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55">
-        <v>59.60976084</v>
-      </c>
-      <c r="C55">
-        <v>12.293728870000001</v>
-      </c>
-      <c r="D55">
-        <f>51.65-0.18-0.4</f>
-        <v>51.07</v>
-      </c>
-      <c r="E55">
-        <f>4.8+0.17+0.55</f>
-        <v>5.52</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56">
-        <v>62.330101769999999</v>
-      </c>
-      <c r="C56">
-        <v>16.987209159999999</v>
-      </c>
-      <c r="D56">
-        <v>42.52</v>
-      </c>
-      <c r="E56">
-        <v>4.78</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57">
-        <v>63.00245108</v>
-      </c>
-      <c r="C57">
-        <v>17.515287409999999</v>
-      </c>
-      <c r="D57">
-        <f>198.2-0.31</f>
-        <v>197.89</v>
-      </c>
-      <c r="E57">
-        <f>9.79+0.25</f>
-        <v>10.039999999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>